--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19205-2024 artfynd.xlsx
+++ b/artfynd/A 19205-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>129425710</v>
       </c>
       <c r="B2" t="n">
-        <v>57071</v>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
